--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_h_10.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_h_10.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.03068610947375319</v>
+        <v>0.02621592296726644</v>
       </c>
       <c r="B2" t="n">
-        <v>0.00846437886825821</v>
+        <v>0.00845820783045732</v>
       </c>
       <c r="C2" t="n">
-        <v>62962770</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>62962770</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>42496605</v>
+        <v>3924814</v>
       </c>
       <c r="L2" t="n">
-        <v>21992737</v>
+        <v>1792737</v>
       </c>
       <c r="M2" t="n">
-        <v>5038527</v>
+        <v>349317</v>
       </c>
       <c r="N2" t="n">
-        <v>201363</v>
+        <v>6303</v>
       </c>
       <c r="O2" t="n">
-        <v>3027443</v>
+        <v>179730</v>
       </c>
       <c r="P2" t="n">
-        <v>1167561</v>
+        <v>57371</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999759197235107</v>
+        <v>0.9999898672103882</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8213366866111755</v>
+        <v>0.740313708782196</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6757699847221375</v>
+        <v>0.5468462705612183</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5928983092308044</v>
+        <v>0.4184128642082214</v>
       </c>
       <c r="U2" t="n">
-        <v>0.215070515871048</v>
+        <v>0.0496893934905529</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6497679352760315</v>
+        <v>0.4672377407550812</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7678503394126892</v>
+        <v>0.635281503200531</v>
       </c>
       <c r="X2" t="n">
-        <v>62962770</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>62962770</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>47766368</v>
+        <v>4750163</v>
       </c>
       <c r="AG2" t="n">
-        <v>29788699</v>
+        <v>3018205</v>
       </c>
       <c r="AH2" t="n">
-        <v>8012790</v>
+        <v>806591</v>
       </c>
       <c r="AI2" t="n">
-        <v>590209</v>
+        <v>59281</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4597208</v>
+        <v>461241</v>
       </c>
       <c r="AK2" t="n">
-        <v>1801493</v>
+        <v>180417</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9558600783348083</v>
+        <v>0.9546809196472168</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9117661118507385</v>
+        <v>0.9128581881523132</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8583323359489441</v>
+        <v>0.8581860065460205</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6618221402168274</v>
+        <v>0.6609027981758118</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020313024520874</v>
+        <v>0.901951789855957</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314513206481934</v>
+        <v>0.9314922094345093</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.008053042851867389</v>
+        <v>0.006739157163470574</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002029700193242254</v>
+        <v>0.002027664927559576</v>
       </c>
       <c r="C3" t="n">
-        <v>1083</v>
+        <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>42496605</v>
+        <v>3924814</v>
       </c>
       <c r="E3" t="n">
-        <v>7111490</v>
+        <v>986777</v>
       </c>
       <c r="F3" t="n">
-        <v>236116</v>
+        <v>42787</v>
       </c>
       <c r="G3" t="n">
-        <v>20714</v>
+        <v>2995</v>
       </c>
       <c r="H3" t="n">
-        <v>16332</v>
+        <v>2500</v>
       </c>
       <c r="I3" t="n">
-        <v>1135</v>
+        <v>217</v>
       </c>
       <c r="J3" t="n">
-        <v>99899713</v>
+        <v>10016558</v>
       </c>
       <c r="K3" t="n">
-        <v>103736346</v>
+        <v>9992747</v>
       </c>
       <c r="L3" t="n">
-        <v>119568522</v>
+        <v>11524885</v>
       </c>
       <c r="M3" t="n">
-        <v>150057402</v>
+        <v>14902199</v>
       </c>
       <c r="N3" t="n">
-        <v>161236398</v>
+        <v>16119247</v>
       </c>
       <c r="O3" t="n">
-        <v>156132235</v>
+        <v>15612756</v>
       </c>
       <c r="P3" t="n">
-        <v>160576390</v>
+        <v>16102858</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8519175052642822</v>
+        <v>0.7912752628326416</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6716670989990234</v>
+        <v>0.5401222109794617</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5390531420707703</v>
+        <v>0.3708815276622772</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2255662530660629</v>
+        <v>0.07018305361270905</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5936232805252075</v>
+        <v>0.3510975539684296</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6035113930702209</v>
+        <v>0.296024352312088</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>47766368</v>
+        <v>4750163</v>
       </c>
       <c r="Z3" t="n">
-        <v>1964194</v>
+        <v>194702</v>
       </c>
       <c r="AA3" t="n">
-        <v>84460</v>
+        <v>8398</v>
       </c>
       <c r="AB3" t="n">
-        <v>67907</v>
+        <v>6808</v>
       </c>
       <c r="AC3" t="n">
-        <v>246</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>99901230</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>110774760</v>
+        <v>11143996</v>
       </c>
       <c r="AG3" t="n">
-        <v>127237766</v>
+        <v>12722349</v>
       </c>
       <c r="AH3" t="n">
-        <v>152194495</v>
+        <v>15254456</v>
       </c>
       <c r="AI3" t="n">
-        <v>161669715</v>
+        <v>16209376</v>
       </c>
       <c r="AJ3" t="n">
-        <v>157264762</v>
+        <v>15767551</v>
       </c>
       <c r="AK3" t="n">
-        <v>160796809</v>
+        <v>16122526</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575589299201965</v>
+        <v>0.9576725363731384</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.909758985042572</v>
+        <v>0.9093356132507324</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8572583794593811</v>
+        <v>0.8563846349716187</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6611504554748535</v>
+        <v>0.6600859761238098</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014239311218262</v>
+        <v>0.9010214805603027</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311903715133667</v>
+        <v>0.9309202432632446</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.06922565257680617</v>
+        <v>0.06090956378945755</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03200867295972447</v>
+        <v>0.03198836053224347</v>
       </c>
       <c r="C4" t="n">
-        <v>109</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>8530224</v>
+        <v>1245241</v>
       </c>
       <c r="E4" t="n">
-        <v>21992737</v>
+        <v>1792737</v>
       </c>
       <c r="F4" t="n">
-        <v>1869152</v>
+        <v>230170</v>
       </c>
       <c r="G4" t="n">
-        <v>110682</v>
+        <v>17649</v>
       </c>
       <c r="H4" t="n">
-        <v>218438</v>
+        <v>30264</v>
       </c>
       <c r="I4" t="n">
-        <v>22165</v>
+        <v>3064</v>
       </c>
       <c r="J4" t="n">
-        <v>1517</v>
+        <v>64</v>
       </c>
       <c r="K4" t="n">
-        <v>9244179</v>
+        <v>1376741</v>
       </c>
       <c r="L4" t="n">
-        <v>10551971</v>
+        <v>1485583</v>
       </c>
       <c r="M4" t="n">
-        <v>3459603</v>
+        <v>485545</v>
       </c>
       <c r="N4" t="n">
-        <v>734902</v>
+        <v>120545</v>
       </c>
       <c r="O4" t="n">
-        <v>1631825</v>
+        <v>204935</v>
       </c>
       <c r="P4" t="n">
-        <v>352997</v>
+        <v>32937</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999879598617554</v>
+        <v>0.9999949336051941</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8363475799560547</v>
+        <v>0.7649466395378113</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6737122535705566</v>
+        <v>0.5434634685516357</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5646950602531433</v>
+        <v>0.3932160437107086</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2201933860778809</v>
+        <v>0.05818440392613411</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6204279661178589</v>
+        <v>0.4009262025356293</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6758339405059814</v>
+        <v>0.4038604199886322</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2060120</v>
+        <v>210743</v>
       </c>
       <c r="Z4" t="n">
-        <v>29788699</v>
+        <v>3018205</v>
       </c>
       <c r="AA4" t="n">
-        <v>827465</v>
+        <v>83377</v>
       </c>
       <c r="AB4" t="n">
-        <v>55180</v>
+        <v>5608</v>
       </c>
       <c r="AC4" t="n">
-        <v>11363</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>680</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2205765</v>
+        <v>225492</v>
       </c>
       <c r="AG4" t="n">
-        <v>2882727</v>
+        <v>288119</v>
       </c>
       <c r="AH4" t="n">
-        <v>1322510</v>
+        <v>133288</v>
       </c>
       <c r="AI4" t="n">
-        <v>301585</v>
+        <v>30416</v>
       </c>
       <c r="AJ4" t="n">
-        <v>499298</v>
+        <v>50140</v>
       </c>
       <c r="AK4" t="n">
-        <v>132578</v>
+        <v>13269</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9567087888717651</v>
+        <v>0.956174373626709</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9107614159584045</v>
+        <v>0.9110934734344482</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8577950596809387</v>
+        <v>0.8572843670845032</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6614861488342285</v>
+        <v>0.6604941487312317</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.901727557182312</v>
+        <v>0.9014863967895508</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.93132084608078</v>
+        <v>0.9312061071395874</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>510522</v>
+        <v>97531</v>
       </c>
       <c r="E5" t="n">
-        <v>2769561</v>
+        <v>381423</v>
       </c>
       <c r="F5" t="n">
-        <v>5038527</v>
+        <v>349317</v>
       </c>
       <c r="G5" t="n">
-        <v>238857</v>
+        <v>32454</v>
       </c>
       <c r="H5" t="n">
-        <v>712143</v>
+        <v>71582</v>
       </c>
       <c r="I5" t="n">
-        <v>77304</v>
+        <v>9535</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>7386870</v>
+        <v>1035298</v>
       </c>
       <c r="L5" t="n">
-        <v>10750770</v>
+        <v>1526395</v>
       </c>
       <c r="M5" t="n">
-        <v>4308468</v>
+        <v>592539</v>
       </c>
       <c r="N5" t="n">
-        <v>691337</v>
+        <v>83505</v>
       </c>
       <c r="O5" t="n">
-        <v>2072497</v>
+        <v>332179</v>
       </c>
       <c r="P5" t="n">
-        <v>767052</v>
+        <v>136434</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.999990701675415</v>
+        <v>0.9999960660934448</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8978838324546814</v>
+        <v>0.8522903919219971</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8691992163658142</v>
+        <v>0.8155510425567627</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9523033499717712</v>
+        <v>0.9339797496795654</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9912427663803101</v>
+        <v>0.9875043034553528</v>
       </c>
       <c r="V5" t="n">
-        <v>0.97725510597229</v>
+        <v>0.9671079516410828</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9931228160858154</v>
+        <v>0.9896279573440552</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>80221</v>
+        <v>8120</v>
       </c>
       <c r="Z5" t="n">
-        <v>856225</v>
+        <v>87176</v>
       </c>
       <c r="AA5" t="n">
-        <v>8012790</v>
+        <v>806591</v>
       </c>
       <c r="AB5" t="n">
-        <v>99697</v>
+        <v>10039</v>
       </c>
       <c r="AC5" t="n">
-        <v>291732</v>
+        <v>29297</v>
       </c>
       <c r="AD5" t="n">
-        <v>6330</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2117107</v>
+        <v>209949</v>
       </c>
       <c r="AG5" t="n">
-        <v>2954808</v>
+        <v>300927</v>
       </c>
       <c r="AH5" t="n">
-        <v>1334205</v>
+        <v>135265</v>
       </c>
       <c r="AI5" t="n">
-        <v>302491</v>
+        <v>30527</v>
       </c>
       <c r="AJ5" t="n">
-        <v>502732</v>
+        <v>50668</v>
       </c>
       <c r="AK5" t="n">
-        <v>133120</v>
+        <v>13388</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734571576118469</v>
+        <v>0.9733342528343201</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641569852828979</v>
+        <v>0.963927686214447</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9836875200271606</v>
+        <v>0.9835542440414429</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.996290922164917</v>
+        <v>0.9962679147720337</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938474297523499</v>
+        <v>0.993826687335968</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983685612678528</v>
+        <v>0.9983675479888916</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>88</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>151063</v>
+        <v>20896</v>
       </c>
       <c r="E6" t="n">
-        <v>204210</v>
+        <v>25813</v>
       </c>
       <c r="F6" t="n">
-        <v>224910</v>
+        <v>27735</v>
       </c>
       <c r="G6" t="n">
-        <v>201363</v>
+        <v>6303</v>
       </c>
       <c r="H6" t="n">
-        <v>100082</v>
+        <v>8043</v>
       </c>
       <c r="I6" t="n">
-        <v>10984</v>
+        <v>1003</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>64965</v>
+        <v>6593</v>
       </c>
       <c r="Z6" t="n">
-        <v>53401</v>
+        <v>5350</v>
       </c>
       <c r="AA6" t="n">
-        <v>109414</v>
+        <v>11081</v>
       </c>
       <c r="AB6" t="n">
-        <v>590209</v>
+        <v>59281</v>
       </c>
       <c r="AC6" t="n">
-        <v>69901</v>
+        <v>7022</v>
       </c>
       <c r="AD6" t="n">
-        <v>4810</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>49544</v>
+        <v>12316</v>
       </c>
       <c r="E7" t="n">
-        <v>425572</v>
+        <v>82492</v>
       </c>
       <c r="F7" t="n">
-        <v>1036086</v>
+        <v>163112</v>
       </c>
       <c r="G7" t="n">
-        <v>319822</v>
+        <v>55141</v>
       </c>
       <c r="H7" t="n">
-        <v>3027443</v>
+        <v>179730</v>
       </c>
       <c r="I7" t="n">
-        <v>241409</v>
+        <v>19118</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8097</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>297857</v>
+        <v>30099</v>
       </c>
       <c r="AB7" t="n">
-        <v>76141</v>
+        <v>7694</v>
       </c>
       <c r="AC7" t="n">
-        <v>4597208</v>
+        <v>461241</v>
       </c>
       <c r="AD7" t="n">
-        <v>120458</v>
+        <v>12057</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>92</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>2826</v>
+        <v>757</v>
       </c>
       <c r="E8" t="n">
-        <v>41138</v>
+        <v>9078</v>
       </c>
       <c r="F8" t="n">
-        <v>93339</v>
+        <v>21741</v>
       </c>
       <c r="G8" t="n">
-        <v>44827</v>
+        <v>12306</v>
       </c>
       <c r="H8" t="n">
-        <v>584830</v>
+        <v>92546</v>
       </c>
       <c r="I8" t="n">
-        <v>1167561</v>
+        <v>57371</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>280</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>810</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3314</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2660</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>126056</v>
+        <v>12679</v>
       </c>
       <c r="AD8" t="n">
-        <v>1801493</v>
+        <v>180417</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
